--- a/Unit_Test_Plan.xlsx
+++ b/Unit_Test_Plan.xlsx
@@ -455,8 +455,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -888,6 +888,166 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Remediation Agent - Corrected Code &amp; Best Practices</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Execute generate_remediations() on flagged SQL injection &amp; secret finding.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Verify generation of executable fix code snippets (parameterized queries, bcrypt, env vars) and OWASP explanations.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Returns enriched findings with remediation summary, corrected code, and grounded best practices.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PR Summary Agent - Health Score &amp; OWASP Mapping</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Execute generate_pr_summary() with severity counts.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Verify accurate Code Health Score formula calculation and OWASP Top 10 category mapping.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Calculates exact health score (0-100) and maps findings to OWASP categories.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Conversational Assistant - RAG Knowledge Base Q&amp;A</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Execute generate_assistant_response() with user query.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Verify retrieval of relevant chunks from ChromaDB and synthesis of grounded secure coding advice.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Returns RAG-grounded response text and reference sources.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Full Milestone 3 LangGraph Orchestration Pipeline</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Invoke orchestrator_app.ainvoke() with initial code state.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Verify full graph execution across Code Analysis, Security, Remediation, and PR Summary nodes.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Returns complete state with remediated findings, PR summary, and health score.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Report Generator - PDF, Markdown, and JSON Export</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Invoke generate_submission_pdf(), generate_submission_markdown(), and generate_submission_json().</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Verify formatted PDF bytes, Markdown string, and JSON dictionary output.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generates valid PDF document, Markdown report, and JSON structure.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Unit_Test_Plan.xlsx
+++ b/Unit_Test_Plan.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,8 +38,19 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -52,8 +63,20 @@
         <bgColor rgb="0068798E"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E3A8A"/>
+        <bgColor rgb="001E3A8A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -75,11 +98,25 @@
         <color rgb="00B0C4DE"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -89,6 +126,21 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -458,591 +510,591 @@
   <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Sl No</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Test Case Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Test Procedure</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Condition to be tested</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="2" t="n">
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Python Code Language Detection</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>Pass a valid Python snippet containing def/import statements to detect_language(code).</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>Verify Python language identification using AST and keyword pattern matching.</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>Returns Language.python accurately.</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="2" t="n">
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Java Code Language Detection</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>Pass a valid Java class snippet with System.out.println to detect_language(code).</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>Verify Java language identification using class and system package keywords.</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>Returns Language.java accurately.</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="2" t="n">
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Language Detection by Filename Extension</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Call detect_language(code, filename='script.py') and filename='Script.java'.</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Verify filename extension takes precedence for unambiguous detection.</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Returns Language.python for .py and Language.java for .java.</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="2" t="n">
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Python Snippet with Syntax Errors</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Pass incomplete Python code with syntax errors to detect_language(code).</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Ensure detector falls back gracefully without throwing syntax exceptions.</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>Returns Language.python without crashing.</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="2" t="n">
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Java Snippet with Syntax Errors</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Pass incomplete Java code missing closing braces to detect_language(code).</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Ensure regex/AST fallback correctly identifies Java structural patterns.</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>Returns Language.java without crashing.</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="2" t="n">
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Code Analysis Agent - Python Quality Scan</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>Execute analyze_code_quality() on Python code with high cyclomatic complexity.</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>Verify code smells, design anti-patterns, and complexity measurement.</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>Returns structured findings list with categories and valid severities.</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="2" t="n">
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Security Agent - Secrets &amp; SQL Injection</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Execute scan_security_vulnerabilities() on Python code with hardcoded password &amp; raw query.</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>Verify detection of OWASP Top 10 security flaws (CWE-798, CWE-89).</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>Identifies hardcoded secrets and SQL injection with CWE IDs.</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="2" t="n">
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Security Agent - Java Command Injection</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>Execute scan_security_vulnerabilities() on Java code with Runtime.exec() calls.</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>Verify Java security scanner flags OS command execution risks.</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>Returns command_injection finding with remediation guidance.</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="2" t="n">
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>LangGraph Multi-Agent Parallel Execution</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>Invoke orchestrator_app.ainvoke() with initial analysis state.</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>Verify parallel execution of Code Analysis and Security nodes and result merging.</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>Merged state contains findings from both analysis agents.</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="2" t="n">
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>RAG Vector Store Document Query</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>Execute similarity query on ChromaDB vector store via POST /api/v1/knowledge-base/query.</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>Verify vector retrieval using HuggingFace BGE embedding model against OWASP docs.</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>Returns top-k relevant documentation chunks with metadata.</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="2" t="n">
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Auth Service Password Hashing &amp; JWT</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Register user, hash password via bcrypt, and issue JWT access token upon login.</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Verify secure password hashing and JWT access token validation.</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>Valid credentials return signed JWT; invalid login returns HTTP 401.</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="2" t="n">
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Code Submission API Validation</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>Submit POST request to /api/v1/submissions/paste with empty source code.</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>Verify Pydantic request body validation for mandatory fields.</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>API returns HTTP 422 Unprocessable Entity with error detail.</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="2" t="n">
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Executive Report Generation</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Invoke generate_report() for a completed code analysis run ID.</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>Verify layout formatting of security findings, scores, and code snippets.</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>Generates executive code review report PDF file.</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Remediation Agent - Corrected Code &amp; Best Practices</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Execute generate_remediations() on flagged SQL injection &amp; secret finding.</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>Verify generation of executable fix code snippets (parameterized queries, bcrypt, env vars) and OWASP explanations.</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>Returns enriched findings with remediation summary, corrected code, and grounded best practices.</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>PR Summary Agent - Health Score &amp; OWASP Mapping</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Execute generate_pr_summary() with severity counts.</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>Verify accurate Code Health Score formula calculation and OWASP Top 10 category mapping.</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>Calculates exact health score (0-100) and maps findings to OWASP categories.</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Conversational Assistant - RAG Knowledge Base Q&amp;A</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>Execute generate_assistant_response() with user query.</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>Verify retrieval of relevant chunks from ChromaDB and synthesis of grounded secure coding advice.</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>Returns RAG-grounded response text and reference sources.</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Full Milestone 3 LangGraph Orchestration Pipeline</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>Invoke orchestrator_app.ainvoke() with initial code state.</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>Verify full graph execution across Code Analysis, Security, Remediation, and PR Summary nodes.</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>Returns complete state with remediated findings, PR summary, and health score.</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Report Generator - PDF, Markdown, and JSON Export</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>Invoke generate_submission_pdf(), generate_submission_markdown(), and generate_submission_json().</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>Verify formatted PDF bytes, Markdown string, and JSON dictionary output.</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>Generates valid PDF document, Markdown report, and JSON structure.</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>

--- a/Unit_Test_Plan.xlsx
+++ b/Unit_Test_Plan.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1100,6 +1100,70 @@
         </is>
       </c>
     </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>User Authentication &amp; JWT Issuance</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Submit POST /api/v1/auth/signup and POST /api/v1/auth/login.</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Verify password hashing via bcrypt and valid JWT token structure.</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Returns 200 OK with signed JWT access token.</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Complete Refactored Code Generation</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Execute generate_full_remediated_code() on vulnerable Python/Java sample.</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Verify generation of complete, executable source file resolving all flagged issues.</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>Returns complete remediated source code file.</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Unit_Test_Plan.xlsx
+++ b/Unit_Test_Plan.xlsx
@@ -116,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -141,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -507,15 +513,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -551,614 +557,734 @@
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>Python Code Language Detection</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>Pass a valid Python snippet containing def/import statements to detect_language(code).</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>Verify Python language identification using AST and keyword pattern matching.</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>Returns Language.python accurately.</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="7" t="n">
+      <c r="A3" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Java Code Language Detection</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>Pass a valid Java class snippet with System.out.println to detect_language(code).</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>Verify Java language identification using class and system package keywords.</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>Returns Language.java accurately.</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Language Detection by Filename Extension</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Call detect_language(code, filename='script.py') and filename='Script.java'.</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Verify filename extension takes precedence for unambiguous detection.</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Returns Language.python for .py and Language.java for .java.</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Python Snippet with Syntax Errors</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Pass incomplete Python code with syntax errors to detect_language(code).</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Ensure detector falls back gracefully without throwing syntax exceptions.</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>Returns Language.python without crashing.</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Java Snippet with Syntax Errors</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Pass incomplete Java code missing closing braces to detect_language(code).</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>Ensure regex/AST fallback correctly identifies Java structural patterns.</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>Returns Language.java without crashing.</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Code Analysis Agent - Python Quality Scan</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Execute analyze_code_quality() on Python code with high cyclomatic complexity.</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>Verify code smells, design anti-patterns, and complexity measurement.</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>Returns structured findings list with categories and valid severities.</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Security Agent - Secrets &amp; SQL Injection</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Execute scan_security_vulnerabilities() on Python code with hardcoded password &amp; raw query.</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>Verify detection of OWASP Top 10 security flaws (CWE-798, CWE-89).</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>Identifies hardcoded secrets and SQL injection with CWE IDs.</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Security Agent - Java Command Injection</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Execute scan_security_vulnerabilities() on Java code with Runtime.exec() calls.</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>Verify Java security scanner flags OS command execution risks.</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>Returns command_injection finding with remediation guidance.</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>LangGraph Multi-Agent Parallel Execution</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Invoke orchestrator_app.ainvoke() with initial analysis state.</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>Verify parallel execution of Code Analysis and Security nodes and result merging.</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>Merged state contains findings from both analysis agents.</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="7" t="n">
+      <c r="A11" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>RAG Vector Store Document Query</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>Execute similarity query on ChromaDB vector store via POST /api/v1/knowledge-base/query.</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>Verify vector retrieval using HuggingFace BGE embedding model against OWASP docs.</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>Returns top-k relevant documentation chunks with metadata.</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Auth Service Password Hashing &amp; JWT</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>Register user, hash password via bcrypt, and issue JWT access token upon login.</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>Verify secure password hashing and JWT access token validation.</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>Valid credentials return signed JWT; invalid login returns HTTP 401.</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="7" t="n">
+      <c r="A13" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>Code Submission API Validation</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>Submit POST request to /api/v1/submissions/paste with empty source code.</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>Verify Pydantic request body validation for mandatory fields.</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>API returns HTTP 422 Unprocessable Entity with error detail.</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Executive Report Generation</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>Invoke generate_report() for a completed code analysis run ID.</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>Verify layout formatting of security findings, scores, and code snippets.</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>Generates executive code review report PDF file.</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>Remediation Agent - Corrected Code &amp; Best Practices</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>Execute generate_remediations() on flagged SQL injection &amp; secret finding.</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>Verify generation of executable fix code snippets (parameterized queries, bcrypt, env vars) and OWASP explanations.</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>Returns enriched findings with remediation summary, corrected code, and grounded best practices.</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>PR Summary Agent - Health Score &amp; OWASP Mapping</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>Execute generate_pr_summary() with severity counts.</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>Verify accurate Code Health Score formula calculation and OWASP Top 10 category mapping.</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>Calculates exact health score (0-100) and maps findings to OWASP categories.</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>Conversational Assistant - RAG Knowledge Base Q&amp;A</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>Execute generate_assistant_response() with user query.</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>Verify retrieval of relevant chunks from ChromaDB and synthesis of grounded secure coding advice.</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>Returns RAG-grounded response text and reference sources.</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>Full Milestone 3 LangGraph Orchestration Pipeline</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>Invoke orchestrator_app.ainvoke() with initial code state.</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>Verify full graph execution across Code Analysis, Security, Remediation, and PR Summary nodes.</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>Returns complete state with remediated findings, PR summary, and health score.</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>Report Generator - PDF, Markdown, and JSON Export</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>Invoke generate_submission_pdf(), generate_submission_markdown(), and generate_submission_json().</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>Verify formatted PDF bytes, Markdown string, and JSON dictionary output.</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>Generates valid PDF document, Markdown report, and JSON structure.</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>User Authentication &amp; JWT Issuance</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>Submit POST /api/v1/auth/signup and POST /api/v1/auth/login.</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>Verify password hashing via bcrypt and valid JWT token structure.</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>Returns 200 OK with signed JWT access token.</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="9" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>Complete Refactored Code Generation</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>Execute generate_full_remediated_code() on vulnerable Python/Java sample.</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>Verify generation of complete, executable source file resolving all flagged issues.</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>Returns complete remediated source code file.</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Post-Generation Remediation AST Validation</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Execute remediation validator on generated Python and Java fix code snippets.</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Verify AST parse tree validity and syntax correctness.</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>Flags invalid syntax and triggers clean fallback remediation.</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Side-by-Side Code Diff Computation</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Pass original vulnerable code and remediated fix code to diff calculator.</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Verify diff line chunk calculation and addition/deletion highlighting.</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>Generates accurate unified and side-by-side diff delta.</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Dynamic Security Policy Finding Filtering</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Toggle scanner modules and severity thresholds in Security Policy panel.</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>Verify real-time filtering of active findings list in review portal.</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>Portal findings update dynamically matching active policy configuration.</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Project Title &amp; MIT License Integration</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Execute E2E test suite and verify generated PDF/Markdown report headers and license file.</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Verify project title matches official name and LICENSE file exists.</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>Reports and API display 'Development of Smart Code Inspection Platform with Vulnerability Detection System Group 2' and MIT License is verified.</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>

--- a/Unit_Test_Plan.xlsx
+++ b/Unit_Test_Plan.xlsx
@@ -116,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -146,6 +146,9 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -516,48 +519,48 @@
   <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Sl No</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Test Case Name</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Test Procedure</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Condition to be tested</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="9" t="n">
+      <c r="A2" s="10" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="10" t="inlineStr">
@@ -580,14 +583,14 @@
           <t>Returns Language.python accurately.</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="9" t="n">
+      <c r="A3" s="10" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="10" t="inlineStr">
@@ -610,14 +613,14 @@
           <t>Returns Language.java accurately.</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="9" t="n">
+      <c r="A4" s="10" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="10" t="inlineStr">
@@ -640,14 +643,14 @@
           <t>Returns Language.python for .py and Language.java for .java.</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="9" t="n">
+      <c r="A5" s="10" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -670,14 +673,14 @@
           <t>Returns Language.python without crashing.</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="9" t="n">
+      <c r="A6" s="10" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -700,14 +703,14 @@
           <t>Returns Language.java without crashing.</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="9" t="n">
+      <c r="A7" s="10" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -730,14 +733,14 @@
           <t>Returns structured findings list with categories and valid severities.</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="9" t="n">
+      <c r="A8" s="10" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
@@ -760,14 +763,14 @@
           <t>Identifies hardcoded secrets and SQL injection with CWE IDs.</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="9" t="n">
+      <c r="A9" s="10" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
@@ -790,14 +793,14 @@
           <t>Returns command_injection finding with remediation guidance.</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="9" t="n">
+      <c r="A10" s="10" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
@@ -820,14 +823,14 @@
           <t>Merged state contains findings from both analysis agents.</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="9" t="n">
+      <c r="A11" s="10" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
@@ -850,14 +853,14 @@
           <t>Returns top-k relevant documentation chunks with metadata.</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="9" t="n">
+      <c r="A12" s="10" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
@@ -880,14 +883,14 @@
           <t>Valid credentials return signed JWT; invalid login returns HTTP 401.</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="9" t="n">
+      <c r="A13" s="10" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
@@ -910,14 +913,14 @@
           <t>API returns HTTP 422 Unprocessable Entity with error detail.</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="9" t="n">
+      <c r="A14" s="10" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
@@ -940,14 +943,14 @@
           <t>Generates executive code review report PDF file.</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -972,14 +975,14 @@
           <t>Returns enriched findings with remediation summary, corrected code, and grounded best practices.</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1004,14 +1007,14 @@
           <t>Calculates exact health score (0-100) and maps findings to OWASP categories.</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -1036,14 +1039,14 @@
           <t>Returns RAG-grounded response text and reference sources.</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -1068,14 +1071,14 @@
           <t>Returns complete state with remediated findings, PR summary, and health score.</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1100,14 +1103,14 @@
           <t>Generates valid PDF document, Markdown report, and JSON structure.</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -1132,14 +1135,14 @@
           <t>Returns 200 OK with signed JWT access token.</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -1164,14 +1167,14 @@
           <t>Returns complete remediated source code file.</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="n">
+      <c r="A22" s="10" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
@@ -1194,14 +1197,14 @@
           <t>Flags invalid syntax and triggers clean fallback remediation.</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F22" s="10" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="n">
+      <c r="A23" s="10" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
@@ -1224,14 +1227,14 @@
           <t>Generates accurate unified and side-by-side diff delta.</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F23" s="10" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="n">
+      <c r="A24" s="10" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
@@ -1254,14 +1257,14 @@
           <t>Portal findings update dynamically matching active policy configuration.</t>
         </is>
       </c>
-      <c r="F24" s="9" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="n">
+      <c r="A25" s="10" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
@@ -1284,7 +1287,7 @@
           <t>Reports and API display 'Development of Smart Code Inspection Platform with Vulnerability Detection System Group 2' and MIT License is verified.</t>
         </is>
       </c>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
